--- a/停电计划.xlsx
+++ b/停电计划.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\cp_sat_scheduler_project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A429C5C4-9142-4355-A8CB-3B244369A388}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B8AD5AD-34C9-4E31-B071-92C69BD0F01F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3040" yWindow="3040" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="停电计划" sheetId="1" r:id="rId1"/>
@@ -405,10 +405,10 @@
     </row>
     <row r="2" spans="1:4" ht="13.4" customHeight="1">
       <c r="A2" s="3">
-        <v>46146</v>
+        <v>46154</v>
       </c>
       <c r="B2" s="3">
-        <v>46147</v>
+        <v>46155</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>15</v>
